--- a/BAK02D.xlsx
+++ b/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="302">
   <si>
     <t/>
   </si>
@@ -253,6 +253,12 @@
     <t>SARI ROTI TWR TOAST</t>
   </si>
   <si>
+    <t>20141862</t>
+  </si>
+  <si>
+    <t>SR RT GANDUM KPS 200</t>
+  </si>
+  <si>
     <t>10006195</t>
   </si>
   <si>
@@ -301,48 +307,48 @@
     <t>SARI ROTI TW.CHIP275</t>
   </si>
   <si>
+    <t>20003593</t>
+  </si>
+  <si>
+    <t>S/ROTI KRIM KEJU 55G</t>
+  </si>
+  <si>
+    <t>10004371</t>
+  </si>
+  <si>
+    <t>SARI ROTI KRIM MOCHA</t>
+  </si>
+  <si>
+    <t>10004372</t>
+  </si>
+  <si>
+    <t>SARI ROTI KRIM COKLT</t>
+  </si>
+  <si>
+    <t>20136101</t>
+  </si>
+  <si>
+    <t>S/ROTI CHOC BERRY50G</t>
+  </si>
+  <si>
+    <t>20137529</t>
+  </si>
+  <si>
+    <t>SARI ROTI CHOCO BNN</t>
+  </si>
+  <si>
+    <t>20137528</t>
+  </si>
+  <si>
+    <t>SARI ROTI DOUBLE CHO</t>
+  </si>
+  <si>
     <t>10004946</t>
   </si>
   <si>
     <t>SARI ROTI COKL.VANLA</t>
   </si>
   <si>
-    <t>20003593</t>
-  </si>
-  <si>
-    <t>S/ROTI KRIM KEJU 55G</t>
-  </si>
-  <si>
-    <t>10004371</t>
-  </si>
-  <si>
-    <t>SARI ROTI KRIM MOCHA</t>
-  </si>
-  <si>
-    <t>10004372</t>
-  </si>
-  <si>
-    <t>SARI ROTI KRIM COKLT</t>
-  </si>
-  <si>
-    <t>20136101</t>
-  </si>
-  <si>
-    <t>S/ROTI CHOC BERRY50G</t>
-  </si>
-  <si>
-    <t>20137529</t>
-  </si>
-  <si>
-    <t>SARI ROTI CHOCO BNN</t>
-  </si>
-  <si>
-    <t>20137528</t>
-  </si>
-  <si>
-    <t>SARI ROTI DOUBLE CHO</t>
-  </si>
-  <si>
     <t>10032089</t>
   </si>
   <si>
@@ -491,6 +497,12 @@
   </si>
   <si>
     <t>SR STMD CHEESE CAKE</t>
+  </si>
+  <si>
+    <t>20141863</t>
+  </si>
+  <si>
+    <t>SR SNDW GNDUM KEJU46</t>
   </si>
   <si>
     <t>20133258</t>
@@ -1297,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1979,10 +1991,10 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2002,7 +2014,7 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2022,7 +2034,7 @@
         <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2042,7 +2054,7 @@
         <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2062,7 +2074,7 @@
         <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2082,7 +2094,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2102,7 +2114,7 @@
         <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2122,7 +2134,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2139,10 +2151,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2162,7 +2174,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2182,7 +2194,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2202,7 +2214,7 @@
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2222,7 +2234,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2242,7 +2254,7 @@
         <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2262,7 +2274,7 @@
         <v>20</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2282,7 +2294,7 @@
         <v>20</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2302,7 +2314,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2322,7 +2334,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2342,7 +2354,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2350,10 +2362,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2362,7 +2374,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2370,10 +2382,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2382,7 +2394,7 @@
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2390,10 +2402,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2402,7 +2414,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2410,19 +2422,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2482,7 +2494,7 @@
         <v>24</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2542,7 +2554,7 @@
         <v>24</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2602,7 +2614,7 @@
         <v>24</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2662,7 +2674,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2722,7 +2734,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2742,7 +2754,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2762,7 +2774,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2782,7 +2794,7 @@
         <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2802,7 +2814,7 @@
         <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2822,7 +2834,7 @@
         <v>24</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2842,7 +2854,7 @@
         <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2859,10 +2871,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2879,10 +2891,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2902,7 +2914,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2919,10 +2931,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2939,10 +2951,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2962,7 +2974,7 @@
         <v>48</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2982,7 +2994,7 @@
         <v>48</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3002,7 +3014,7 @@
         <v>48</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3019,10 +3031,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3039,10 +3051,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3062,7 +3074,7 @@
         <v>51</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3082,18 +3094,18 @@
         <v>51</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>196</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3102,7 +3114,7 @@
         <v>51</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3110,10 +3122,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3122,10 +3134,10 @@
         <v>51</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3142,7 +3154,7 @@
         <v>51</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3162,7 +3174,7 @@
         <v>51</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3179,10 +3191,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3199,10 +3211,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3219,13 +3231,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3239,10 +3251,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3259,13 +3271,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3279,10 +3291,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3299,10 +3311,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3319,10 +3331,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3339,10 +3351,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3359,10 +3371,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3379,10 +3391,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3399,10 +3411,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3419,10 +3431,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3439,10 +3451,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3459,10 +3471,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3479,10 +3491,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3499,10 +3511,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3519,10 +3531,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3539,10 +3551,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3559,10 +3571,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3579,10 +3591,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3599,10 +3611,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3619,10 +3631,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3639,10 +3651,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3659,10 +3671,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3679,10 +3691,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3699,10 +3711,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3719,10 +3731,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3739,10 +3751,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3759,10 +3771,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3779,10 +3791,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3799,10 +3811,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3819,10 +3831,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3830,19 +3842,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>274</v>
+        <v>126</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3850,19 +3862,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3870,19 +3882,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3890,19 +3902,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3910,19 +3922,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -3930,59 +3942,59 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F132" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F133" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>21</v>
@@ -3999,10 +4011,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>21</v>
@@ -4019,12 +4031,52 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E136" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="F138" s="1" t="s">
         <v>21</v>
       </c>
     </row>
